--- a/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3555" uniqueCount="603">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,16 +656,6 @@
     <t>檢驗檢查分類</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.id</t>
   </si>
   <si>
@@ -938,6 +928,24 @@
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/vital-signs-tw</t>
   </si>
   <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
     <t>Observation.code.id</t>
   </si>
   <si>
@@ -967,12 +975,6 @@
   </si>
   <si>
     <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
   </si>
   <si>
     <t>Observation.code.coding.id</t>
@@ -1137,7 +1139,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1148,9 +1150,6 @@
   </si>
   <si>
     <t>通常檢驗檢查的對象是一位病人或一群病人、地點或設備，檢驗檢查對象與直接測量內容之間的區別在observation.code已具體說明（例如： 「血糖」），不需要使用這個資料項目（focus）單獨表示。如果需要參照檢體，則使用specimen，如果需要一個代碼而不是一個resource，則使用bodysite來表示bodysites或標準擴充focusCode。</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1371,6 +1370,13 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
+    <t>obs-6
+vs-2</t>
+  </si>
+  <si>
+    <t>value.nullFlavor</t>
+  </si>
+  <si>
     <t>Observation.interpretation</t>
   </si>
   <si>
@@ -1396,6 +1402,18 @@
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
+    <t>&lt; 260245000 |Findings values|</t>
+  </si>
+  <si>
+    <t>OBX-8</t>
+  </si>
+  <si>
+    <t>interpretationCode</t>
+  </si>
+  <si>
+    <t>363713009 |Has interpretation|</t>
+  </si>
+  <si>
     <t>Observation.note</t>
   </si>
   <si>
@@ -1440,6 +1458,18 @@
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t>&lt; 123037004 |Body structure|</t>
+  </si>
+  <si>
+    <t>OBX-20</t>
+  </si>
+  <si>
+    <t>targetSiteCode</t>
+  </si>
+  <si>
+    <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1459,6 +1489,12 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+  </si>
+  <si>
+    <t>OBX-17</t>
+  </si>
+  <si>
+    <t>methodCode</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -1493,7 +1529,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1574,7 +1610,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1624,6 +1660,18 @@
     <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
+    <t>&lt; 260245000 |Findings values| OR  +&lt; 365860008 |General clinical state finding| +OR +&lt; 250171008 |Clinical history or observation findings| OR  +&lt; 415229000 |Racial group| OR +&lt; 365400002 |Finding of puberty stage| OR+&lt; 443938003 |Procedure carried out on subject|</t>
+  </si>
+  <si>
+    <t>OBX-10</t>
+  </si>
+  <si>
     <t>Observation.referenceRange.appliesTo</t>
   </si>
   <si>
@@ -1787,6 +1835,10 @@
     <t>代碼指明檢驗檢查的名稱；可參考所綁定值集，但此值集只是針對這個欄位的一個可能值的範例，不預期也不鼓勵使用者一定要使用此值集的代碼。</t>
   </si>
   <si>
+    <t>&lt; 363787002 |Observable entity| OR +&lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -1825,6 +1877,10 @@
   </si>
   <si>
     <t>代碼指明為什麼結果（Observation.value[x]）缺少；應填入所綁定值集中適合的代碼，確定無適合的代碼才可以使用其他值集的代碼來表示。</t>
+  </si>
+  <si>
+    <t>obs-6
+vs-3</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2198,7 +2254,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.26953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -4115,7 +4171,7 @@
         <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>104</v>
@@ -4127,13 +4183,13 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -4141,10 +4197,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4167,13 +4223,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4224,7 +4280,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4248,7 +4304,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4259,10 +4315,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4291,7 +4347,7 @@
         <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>142</v>
@@ -4332,10 +4388,10 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4344,7 +4400,7 @@
         <v>199</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4368,7 +4424,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4379,10 +4435,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4405,19 +4461,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4466,7 +4522,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4487,10 +4543,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -4501,10 +4557,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4527,13 +4583,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4584,7 +4640,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4608,7 +4664,7 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4619,10 +4675,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4651,7 +4707,7 @@
         <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>142</v>
@@ -4692,10 +4748,10 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
@@ -4704,7 +4760,7 @@
         <v>199</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4728,7 +4784,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4739,10 +4795,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4768,23 +4824,23 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>20</v>
@@ -4826,7 +4882,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4847,10 +4903,10 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -4861,10 +4917,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4887,16 +4943,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4946,7 +5002,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4967,10 +5023,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -4981,10 +5037,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5010,21 +5066,21 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>20</v>
@@ -5066,7 +5122,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5087,10 +5143,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5101,10 +5157,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5127,17 +5183,17 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5186,7 +5242,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5207,10 +5263,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5221,10 +5277,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5247,19 +5303,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5308,7 +5364,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5329,10 +5385,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5343,10 +5399,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5369,19 +5425,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5430,7 +5486,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5451,10 +5507,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5465,14 +5521,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5488,22 +5544,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>194</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5528,13 +5584,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5552,7 +5608,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5561,36 +5617,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5613,13 +5669,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5670,7 +5726,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5694,7 +5750,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5705,10 +5761,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5734,10 +5790,10 @@
         <v>139</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5776,10 +5832,10 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
@@ -5788,7 +5844,7 @@
         <v>199</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5823,10 +5879,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5846,22 +5902,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5910,7 +5966,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5919,7 +5975,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -5931,10 +5987,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5945,10 +6001,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5971,13 +6027,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6028,7 +6084,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6052,7 +6108,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6063,10 +6119,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6092,13 +6148,13 @@
         <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6136,10 +6192,10 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
@@ -6148,7 +6204,7 @@
         <v>199</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6183,10 +6239,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6212,16 +6268,16 @@
         <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6231,7 +6287,7 @@
         <v>20</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>20</v>
@@ -6270,7 +6326,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6291,10 +6347,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6305,10 +6361,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6331,16 +6387,16 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6390,7 +6446,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6411,10 +6467,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6425,10 +6481,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6454,14 +6510,14 @@
         <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6471,7 +6527,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -6510,7 +6566,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6531,10 +6587,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6545,10 +6601,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6571,17 +6627,17 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6591,7 +6647,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -6630,7 +6686,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6651,10 +6707,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6665,10 +6721,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6691,19 +6747,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6752,7 +6808,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6773,10 +6829,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6787,10 +6843,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6813,19 +6869,19 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6874,7 +6930,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6895,10 +6951,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -6909,10 +6965,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6935,19 +6991,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6996,7 +7052,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7011,19 +7067,19 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -7031,10 +7087,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7057,13 +7113,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7114,7 +7170,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7138,7 +7194,7 @@
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7149,10 +7205,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7181,7 +7237,7 @@
         <v>140</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>142</v>
@@ -7222,10 +7278,10 @@
         <v>20</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>20</v>
@@ -7234,7 +7290,7 @@
         <v>199</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7258,7 +7314,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7269,10 +7325,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7295,16 +7351,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7354,7 +7410,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7363,7 +7419,7 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
@@ -7389,10 +7445,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7418,13 +7474,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7450,13 +7506,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7474,7 +7530,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7509,10 +7565,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7538,13 +7594,13 @@
         <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7594,7 +7650,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7618,7 +7674,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7629,10 +7685,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7655,16 +7711,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7714,7 +7770,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7749,10 +7805,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7775,16 +7831,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7834,7 +7890,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7855,13 +7911,13 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>365</v>
+        <v>296</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>366</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>20</v>
@@ -8379,13 +8435,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8436,7 +8492,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8460,7 +8516,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8503,7 +8559,7 @@
         <v>140</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>142</v>
@@ -8544,10 +8600,10 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
@@ -8556,7 +8612,7 @@
         <v>199</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8580,7 +8636,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8617,16 +8673,16 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8676,7 +8732,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8685,7 +8741,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -8740,13 +8796,13 @@
         <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8772,13 +8828,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8796,7 +8852,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8860,13 +8916,13 @@
         <v>151</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8916,7 +8972,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8940,7 +8996,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8977,16 +9033,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9036,7 +9092,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9134,7 +9190,7 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>421</v>
@@ -9256,7 +9312,7 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>433</v>
@@ -9289,7 +9345,7 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>205</v>
+        <v>435</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9301,10 +9357,10 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>207</v>
+        <v>436</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9315,14 +9371,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9344,16 +9400,16 @@
         <v>191</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9378,13 +9434,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9402,7 +9458,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9411,7 +9467,7 @@
         <v>81</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>104</v>
@@ -9420,27 +9476,27 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>20</v>
+        <v>445</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>206</v>
+        <v>446</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>20</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9463,19 +9519,19 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9524,7 +9580,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9545,10 +9601,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9559,10 +9615,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9588,13 +9644,13 @@
         <v>191</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9620,13 +9676,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -9644,7 +9700,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9653,7 +9709,7 @@
         <v>92</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>104</v>
@@ -9662,27 +9718,27 @@
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>20</v>
+        <v>463</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>206</v>
+        <v>464</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>207</v>
+        <v>465</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>20</v>
+        <v>466</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9708,16 +9764,16 @@
         <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9742,13 +9798,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9766,7 +9822,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9775,7 +9831,7 @@
         <v>92</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>104</v>
@@ -9787,10 +9843,10 @@
         <v>20</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>206</v>
+        <v>474</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>207</v>
+        <v>475</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -9801,10 +9857,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9827,16 +9883,16 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9886,7 +9942,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9904,27 +9960,27 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>472</v>
+        <v>484</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9947,16 +10003,16 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -10006,7 +10062,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10024,27 +10080,27 @@
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>481</v>
+        <v>493</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10067,19 +10123,19 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10128,7 +10184,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10140,7 +10196,7 @@
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
@@ -10149,10 +10205,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10163,10 +10219,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10189,13 +10245,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10246,7 +10302,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10270,7 +10326,7 @@
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10281,10 +10337,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10313,7 +10369,7 @@
         <v>140</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>142</v>
@@ -10366,7 +10422,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10390,7 +10446,7 @@
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10401,14 +10457,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10430,10 +10486,10 @@
         <v>139</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>142</v>
@@ -10488,7 +10544,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10523,10 +10579,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10549,13 +10605,13 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10606,7 +10662,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10615,7 +10671,7 @@
         <v>92</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>104</v>
@@ -10627,10 +10683,10 @@
         <v>20</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
@@ -10641,10 +10697,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10667,13 +10723,13 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10724,7 +10780,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10733,7 +10789,7 @@
         <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>104</v>
@@ -10745,10 +10801,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10759,10 +10815,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10788,16 +10844,16 @@
         <v>191</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>20</v>
@@ -10825,10 +10881,10 @@
         <v>117</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10846,7 +10902,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10855,7 +10911,7 @@
         <v>92</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>104</v>
@@ -10864,13 +10920,13 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>206</v>
+        <v>528</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
@@ -10881,10 +10937,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10910,16 +10966,16 @@
         <v>191</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10944,13 +11000,13 @@
         <v>20</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -10968,7 +11024,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10977,7 +11033,7 @@
         <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>104</v>
@@ -10986,13 +11042,13 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>20</v>
+        <v>527</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>206</v>
+        <v>528</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11003,10 +11059,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11029,17 +11085,17 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11088,7 +11144,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11112,7 +11168,7 @@
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11123,10 +11179,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11149,13 +11205,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>529</v>
+        <v>543</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>530</v>
+        <v>544</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11206,7 +11262,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>528</v>
+        <v>542</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11227,10 +11283,10 @@
         <v>20</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>531</v>
+        <v>545</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11241,10 +11297,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11267,16 +11323,16 @@
         <v>93</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>533</v>
+        <v>547</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>534</v>
+        <v>548</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>535</v>
+        <v>549</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>536</v>
+        <v>550</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11326,7 +11382,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11347,10 +11403,10 @@
         <v>20</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>538</v>
+        <v>552</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11361,10 +11417,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>539</v>
+        <v>553</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11387,13 +11443,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11444,7 +11500,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11468,7 +11524,7 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11479,10 +11535,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11511,7 +11567,7 @@
         <v>140</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>142</v>
@@ -11552,10 +11608,10 @@
         <v>20</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>20</v>
@@ -11564,7 +11620,7 @@
         <v>199</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11588,7 +11644,7 @@
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11599,10 +11655,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>541</v>
+        <v>555</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11625,16 +11681,16 @@
         <v>93</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11684,7 +11740,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11693,7 +11749,7 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
@@ -11719,10 +11775,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>543</v>
+        <v>557</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11748,13 +11804,13 @@
         <v>106</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11780,13 +11836,13 @@
         <v>20</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>20</v>
@@ -11804,7 +11860,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11839,10 +11895,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>544</v>
+        <v>558</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11868,13 +11924,13 @@
         <v>151</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11924,7 +11980,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11948,7 +12004,7 @@
         <v>20</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -11959,10 +12015,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>545</v>
+        <v>559</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11985,16 +12041,16 @@
         <v>93</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12044,7 +12100,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12079,10 +12135,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12105,16 +12161,16 @@
         <v>93</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>547</v>
+        <v>561</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>549</v>
+        <v>563</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>550</v>
+        <v>564</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12164,7 +12220,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>546</v>
+        <v>560</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12185,10 +12241,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>537</v>
+        <v>551</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>551</v>
+        <v>565</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12199,10 +12255,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12225,19 +12281,19 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>553</v>
+        <v>567</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>554</v>
+        <v>568</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>555</v>
+        <v>569</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12286,7 +12342,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>552</v>
+        <v>566</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12298,7 +12354,7 @@
         <v>20</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>20</v>
@@ -12307,10 +12363,10 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>558</v>
+        <v>572</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>559</v>
+        <v>573</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12321,10 +12377,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>560</v>
+        <v>574</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12347,13 +12403,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12404,7 +12460,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12428,7 +12484,7 @@
         <v>20</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12439,10 +12495,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>561</v>
+        <v>575</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12471,7 +12527,7 @@
         <v>140</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>142</v>
@@ -12524,7 +12580,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12548,7 +12604,7 @@
         <v>20</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12559,14 +12615,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>562</v>
+        <v>576</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12588,10 +12644,10 @@
         <v>139</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>142</v>
@@ -12646,7 +12702,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12681,10 +12737,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12704,22 +12760,22 @@
         <v>20</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>565</v>
+        <v>579</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12744,13 +12800,13 @@
         <v>20</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>20</v>
@@ -12768,7 +12824,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>563</v>
+        <v>577</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>92</v>
@@ -12777,7 +12833,7 @@
         <v>92</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>104</v>
@@ -12786,16 +12842,16 @@
         <v>20</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>20</v>
+        <v>582</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>20</v>
@@ -12803,10 +12859,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12832,16 +12888,16 @@
         <v>416</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>20</v>
@@ -12866,13 +12922,13 @@
         <v>20</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -12890,7 +12946,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12899,7 +12955,7 @@
         <v>92</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>104</v>
@@ -12908,7 +12964,7 @@
         <v>20</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>425</v>
@@ -12925,10 +12981,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12954,10 +13010,10 @@
         <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>431</v>
@@ -12988,10 +13044,10 @@
         <v>20</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="Z90" t="s" s="2">
         <v>434</v>
@@ -13012,7 +13068,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13021,7 +13077,7 @@
         <v>92</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>205</v>
+        <v>596</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>104</v>
@@ -13033,10 +13089,10 @@
         <v>20</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>207</v>
+        <v>436</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13047,14 +13103,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13076,16 +13132,16 @@
         <v>191</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>582</v>
+        <v>598</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13110,13 +13166,13 @@
         <v>20</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>583</v>
+        <v>599</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>20</v>
@@ -13134,7 +13190,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>581</v>
+        <v>597</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13143,7 +13199,7 @@
         <v>81</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>104</v>
@@ -13152,27 +13208,27 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>20</v>
+        <v>445</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>206</v>
+        <v>446</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>207</v>
+        <v>447</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>20</v>
+        <v>448</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13198,16 +13254,16 @@
         <v>82</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>585</v>
+        <v>601</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>586</v>
+        <v>602</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13256,7 +13312,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>584</v>
+        <v>600</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13277,10 +13333,10 @@
         <v>20</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSignsPanel.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
